--- a/results/ntnu_datasets_postures.xlsx
+++ b/results/ntnu_datasets_postures.xlsx
@@ -621,31 +621,31 @@
         <v>46</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8331971508568404</v>
+        <v>0.8332101967812183</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7718512446753655</v>
+        <v>0.7718629164714981</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8945430570383154</v>
+        <v>0.8945574770909386</v>
       </c>
       <c r="G5" t="n">
         <v>46</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9305759813754255</v>
+        <v>0.9305906421769063</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9082165094406701</v>
+        <v>0.9082404206642716</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9529354533101809</v>
+        <v>0.9529408636895411</v>
       </c>
       <c r="K5" t="n">
         <v>46</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09737883051858509</v>
+        <v>0.09738044539568802</v>
       </c>
     </row>
     <row r="6">
@@ -663,31 +663,31 @@
         <v>46</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9343879689138107</v>
+        <v>0.934420097613315</v>
       </c>
       <c r="E6" t="n">
-        <v>0.911005088327758</v>
+        <v>0.9110284274855189</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9577708494998635</v>
+        <v>0.9578117677411111</v>
       </c>
       <c r="G6" t="n">
         <v>46</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9353927243844098</v>
+        <v>0.935448756683569</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9172464092011434</v>
+        <v>0.9172764653988218</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9535390395676762</v>
+        <v>0.9536210479683161</v>
       </c>
       <c r="K6" t="n">
         <v>46</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001004755470599084</v>
+        <v>0.001028659070253957</v>
       </c>
     </row>
     <row r="7">
@@ -823,13 +823,13 @@
         <v>31</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08301344095772104</v>
+        <v>0.08296801857322053</v>
       </c>
       <c r="E2" t="n">
-        <v>0.005438331754728035</v>
+        <v>0.005440767781387953</v>
       </c>
       <c r="F2" t="n">
-        <v>0.160588550160714</v>
+        <v>0.1604952693650531</v>
       </c>
       <c r="G2" t="n">
         <v>25</v>
@@ -847,7 +847,7 @@
         <v>25</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8177425408506306</v>
+        <v>0.817787963235131</v>
       </c>
     </row>
     <row r="3">
@@ -865,10 +865,10 @@
         <v>31</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7291967291967292</v>
+        <v>0.7290167865707433</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2716637084614871</v>
+        <v>0.2712995648692514</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -889,7 +889,7 @@
         <v>25</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2372040177397094</v>
+        <v>0.2373839603656953</v>
       </c>
     </row>
     <row r="4">
@@ -949,31 +949,31 @@
         <v>31</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7871614936115618</v>
+        <v>0.7871495400799374</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7205978729040139</v>
+        <v>0.720589645944151</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8537251143191098</v>
+        <v>0.8537094342157239</v>
       </c>
       <c r="G5" t="n">
         <v>30</v>
       </c>
       <c r="H5" t="n">
-        <v>0.913345908237238</v>
+        <v>0.9133258875617672</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8614259470406878</v>
+        <v>0.8614062203322107</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9652658694337883</v>
+        <v>0.9652455547913238</v>
       </c>
       <c r="K5" t="n">
         <v>30</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1261844146256762</v>
+        <v>0.1261763474818298</v>
       </c>
     </row>
     <row r="6">
@@ -991,31 +991,31 @@
         <v>31</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7157557065267215</v>
+        <v>0.7157381941903338</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6274742201092971</v>
+        <v>0.6274619561162262</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8040371929441459</v>
+        <v>0.8040144322644414</v>
       </c>
       <c r="G6" t="n">
         <v>30</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9334847663594895</v>
+        <v>0.9334416172815007</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8814304481373806</v>
+        <v>0.8813962377618156</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9855390845815984</v>
+        <v>0.9854869968011857</v>
       </c>
       <c r="K6" t="n">
         <v>30</v>
       </c>
       <c r="L6" t="n">
-        <v>0.217729059832768</v>
+        <v>0.2177034230911669</v>
       </c>
     </row>
     <row r="7">
@@ -1033,25 +1033,25 @@
         <v>31</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9504591097609226</v>
+        <v>0.9504537704475583</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9054135025343342</v>
+        <v>0.9054089842566275</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9955047169875111</v>
+        <v>0.9954985566384891</v>
       </c>
       <c r="G7" t="n">
         <v>30</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9261123173670582</v>
+        <v>0.9261069780536939</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8656193267257694</v>
+        <v>0.8656149046745678</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9866053080083471</v>
+        <v>0.98659905143282</v>
       </c>
       <c r="K7" t="n">
         <v>30</v>
